--- a/artfynd/A 21672-2023 artfynd.xlsx
+++ b/artfynd/A 21672-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 21672-2023 artfynd.xlsx
+++ b/artfynd/A 21672-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62023266</v>
+        <v>62023268</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>530398.2169954295</v>
+        <v>530174</v>
       </c>
       <c r="R2" t="n">
-        <v>7155511.60305655</v>
+        <v>7155395</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-10-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +767,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # sälg</t>
+          <t>1 substratenheter # låga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62023267</v>
+        <v>62023269</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>530281.8819446142</v>
+        <v>530174</v>
       </c>
       <c r="R3" t="n">
-        <v>7155460.059612333</v>
+        <v>7155395</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +853,9 @@
           <t>2016-10-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-10-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +877,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # sälg</t>
+          <t>1 substratenheter # låga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -925,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62023269</v>
+        <v>62023266</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>530173.8712187089</v>
+        <v>530398</v>
       </c>
       <c r="R4" t="n">
-        <v>7155394.821492305</v>
+        <v>7155512</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,19 +963,9 @@
           <t>2016-10-10</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-10-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,7 +987,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>1 substratenheter # låga</t>
+          <t>1 substratenheter # sälg</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1050,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62023268</v>
+        <v>62023267</v>
       </c>
       <c r="B5" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,21 +1016,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>510</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>530173.8712187089</v>
+        <v>530282</v>
       </c>
       <c r="R5" t="n">
-        <v>7155394.821492305</v>
+        <v>7155460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1123,19 +1073,9 @@
           <t>2016-10-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-10-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1097,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>1 substratenheter # låga</t>
+          <t>1 substratenheter # sälg</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 21672-2023 artfynd.xlsx
+++ b/artfynd/A 21672-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62023268</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62023269</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62023266</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,8 +1132,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62023267</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>